--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AdamMo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E46A81-E34C-4E14-83F9-F53CA910D3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D9CA1B-CF64-4BAA-A41D-1FF7D04DA86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-936" yWindow="1332" windowWidth="30720" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-780" yWindow="1608" windowWidth="30720" windowHeight="14160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
   <si>
     <t>玩家初始分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -119,6 +120,10 @@
   </si>
   <si>
     <t>敌人总分-精英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x2点位</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1288,4 +1293,850 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90AC4D0A-3569-4D64-9EA4-6DBEB5A45CA9}">
+  <dimension ref="A1:Q44"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B2" s="1">
+        <f>(B3+B4)/2</f>
+        <v>500</v>
+      </c>
+      <c r="C2" s="1">
+        <f t="shared" ref="C2:G2" si="0">(C3+C4)/2</f>
+        <v>650</v>
+      </c>
+      <c r="D2" s="1">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="E2" s="1">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="G2" s="1">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="H2" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I2" s="1">
+        <v>4500</v>
+      </c>
+      <c r="J2" s="1">
+        <v>500</v>
+      </c>
+      <c r="K2" s="1">
+        <v>600</v>
+      </c>
+      <c r="L2" s="1">
+        <v>950</v>
+      </c>
+      <c r="M2" s="1">
+        <v>950</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1100</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1300</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>300</v>
+      </c>
+      <c r="C3" s="1">
+        <v>300</v>
+      </c>
+      <c r="D3" s="1">
+        <v>700</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1500</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1">
+        <v>700</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1200</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>500</v>
+      </c>
+      <c r="D5" s="1">
+        <v>900</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1250</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1500</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <f>5</f>
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <f>A2</f>
+        <v>5000</v>
+      </c>
+      <c r="D10" s="1">
+        <f>I2</f>
+        <v>4500</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1">
+        <f>B10+1</f>
+        <v>6</v>
+      </c>
+      <c r="C11" s="1">
+        <f>C10+B$2</f>
+        <v>5500</v>
+      </c>
+      <c r="D11" s="1">
+        <f>D10+J$2</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" ref="B12:B25" si="1">B11+1</f>
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" ref="C12:C14" si="2">C11+B$2</f>
+        <v>6000</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" ref="D12:D14" si="3">D11+J$2</f>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="2"/>
+        <v>6500</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="3"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="2"/>
+        <v>7000</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="3"/>
+        <v>6500</v>
+      </c>
+      <c r="E14" s="1">
+        <f>D14*1.25</f>
+        <v>8125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C15" s="1">
+        <f>C14+C$2</f>
+        <v>7650</v>
+      </c>
+      <c r="D15" s="1">
+        <f>D14+K$2</f>
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" ref="C16:C19" si="4">C15+C$2</f>
+        <v>8300</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" ref="D16:D19" si="5">D15+K$2</f>
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="4"/>
+        <v>8950</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="5"/>
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="4"/>
+        <v>9600</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="5"/>
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>10</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="4"/>
+        <v>10250</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="5"/>
+        <v>9500</v>
+      </c>
+      <c r="E19" s="1">
+        <f>D19*1.25</f>
+        <v>11875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C20" s="1">
+        <f>C19+D$2</f>
+        <v>11200</v>
+      </c>
+      <c r="D20" s="1">
+        <f>D19+L$2</f>
+        <v>10450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1">
+        <f>B20+1</f>
+        <v>16</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" ref="C21:C24" si="6">C20+D$2</f>
+        <v>12150</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" ref="D21:D24" si="7">D20+L$2</f>
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="6"/>
+        <v>13100</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="7"/>
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="6"/>
+        <v>14050</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="7"/>
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="7"/>
+        <v>14250</v>
+      </c>
+      <c r="E24" s="1">
+        <f>D24*1.25</f>
+        <v>17812.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>16</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="C25" s="1">
+        <f>C24+E$2-B$2</f>
+        <v>15750</v>
+      </c>
+      <c r="D25" s="1">
+        <f>D24+M$2</f>
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>17</v>
+      </c>
+      <c r="B26" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C26" s="1">
+        <f>C25+E$2-B$2</f>
+        <v>16500</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" ref="D26:D28" si="8">D25+M$2</f>
+        <v>16150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>18</v>
+      </c>
+      <c r="B27" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" ref="C27:C28" si="9">C26+E$2-B$2</f>
+        <v>17250</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="8"/>
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>19</v>
+      </c>
+      <c r="B28" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="9"/>
+        <v>18000</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="8"/>
+        <v>18050</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>20</v>
+      </c>
+      <c r="B29" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="1">
+        <f>C28+F$2-B$2</f>
+        <v>19100</v>
+      </c>
+      <c r="D29" s="1">
+        <f>D28+N$2</f>
+        <v>19050</v>
+      </c>
+      <c r="E29" s="1">
+        <f>D29*1.25</f>
+        <v>23812.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>21</v>
+      </c>
+      <c r="B30" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C30" s="1">
+        <f>C29+F$2-C$2</f>
+        <v>20050</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" ref="D30:D33" si="10">D29+N$2</f>
+        <v>20050</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>22</v>
+      </c>
+      <c r="B31" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" ref="C31:C34" si="11">C30+E$2-C$2</f>
+        <v>20650</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="10"/>
+        <v>21050</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>23</v>
+      </c>
+      <c r="B32" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="11"/>
+        <v>21250</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="10"/>
+        <v>22050</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>24</v>
+      </c>
+      <c r="B33" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="11"/>
+        <v>21850</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="10"/>
+        <v>23050</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>25</v>
+      </c>
+      <c r="B34" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="11"/>
+        <v>22450</v>
+      </c>
+      <c r="D34" s="1">
+        <f>D33+O$2</f>
+        <v>24150</v>
+      </c>
+      <c r="E34" s="1">
+        <f>D34*1.25</f>
+        <v>30187.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>26</v>
+      </c>
+      <c r="B35" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C35" s="1">
+        <f>C34+G$2-C$2</f>
+        <v>23800</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" ref="D35:D38" si="12">D34+O$2</f>
+        <v>25250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>27</v>
+      </c>
+      <c r="B36" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" ref="C36:C39" si="13">C35+G$2-C$2</f>
+        <v>25150</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="12"/>
+        <v>26350</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>28</v>
+      </c>
+      <c r="B37" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" si="13"/>
+        <v>26500</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="12"/>
+        <v>27450</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>29</v>
+      </c>
+      <c r="B38" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" si="13"/>
+        <v>27850</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="12"/>
+        <v>28550</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>30</v>
+      </c>
+      <c r="B39" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" si="13"/>
+        <v>29200</v>
+      </c>
+      <c r="D39" s="1">
+        <f>D38+P$2</f>
+        <v>29850</v>
+      </c>
+      <c r="E39" s="1">
+        <f>D39*1.25</f>
+        <v>37312.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>31</v>
+      </c>
+      <c r="B40" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C40" s="1">
+        <f>C39+H$2-D$2</f>
+        <v>30750</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" ref="D40:D44" si="14">D39+P$2</f>
+        <v>31150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>32</v>
+      </c>
+      <c r="B41" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" ref="C41:C44" si="15">C40+H$2-D$2</f>
+        <v>32300</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="14"/>
+        <v>32450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>33</v>
+      </c>
+      <c r="B42" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="15"/>
+        <v>33850</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="14"/>
+        <v>33750</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>34</v>
+      </c>
+      <c r="B43" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" si="15"/>
+        <v>35400</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="14"/>
+        <v>35050</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>35</v>
+      </c>
+      <c r="B44" s="1">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="15"/>
+        <v>36950</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="14"/>
+        <v>36350</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D9CA1B-CF64-4BAA-A41D-1FF7D04DA86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2456B655-3896-491E-AC1E-97E86E20C70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-780" yWindow="1608" windowWidth="30720" windowHeight="14160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1395,10 +1395,10 @@
         <v>4500</v>
       </c>
       <c r="J2" s="1">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="K2" s="1">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="L2" s="1">
         <v>950</v>
@@ -1407,7 +1407,7 @@
         <v>950</v>
       </c>
       <c r="N2" s="1">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="O2" s="1">
         <v>1100</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D11" s="1">
         <f>D10+J$2</f>
-        <v>5000</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ref="D12:D14" si="3">D11+J$2</f>
-        <v>5500</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="3"/>
-        <v>6000</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1597,11 +1597,11 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="3"/>
-        <v>6500</v>
+        <v>6300</v>
       </c>
       <c r="E14" s="1">
         <f>D14*1.25</f>
-        <v>8125</v>
+        <v>7875</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D15" s="1">
         <f>D14+K$2</f>
-        <v>7100</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ref="D16:D19" si="5">D15+K$2</f>
-        <v>7700</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="5"/>
-        <v>8300</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" si="5"/>
-        <v>8900</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="5"/>
-        <v>9500</v>
+        <v>10550</v>
       </c>
       <c r="E19" s="1">
         <f>D19*1.25</f>
-        <v>11875</v>
+        <v>13187.5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="D20" s="1">
         <f>D19+L$2</f>
-        <v>10450</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:D24" si="7">D20+L$2</f>
-        <v>11400</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" si="7"/>
-        <v>12350</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" si="7"/>
-        <v>13300</v>
+        <v>14350</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,11 +1775,11 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" si="7"/>
-        <v>14250</v>
+        <v>15300</v>
       </c>
       <c r="E24" s="1">
         <f>D24*1.25</f>
-        <v>17812.5</v>
+        <v>19125</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D25" s="1">
         <f>D24+M$2</f>
-        <v>15200</v>
+        <v>16250</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ref="D26:D28" si="8">D25+M$2</f>
-        <v>16150</v>
+        <v>17200</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" si="8"/>
-        <v>17100</v>
+        <v>18150</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" si="8"/>
-        <v>18050</v>
+        <v>19100</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1864,11 +1864,11 @@
       </c>
       <c r="D29" s="1">
         <f>D28+N$2</f>
-        <v>19050</v>
+        <v>20050</v>
       </c>
       <c r="E29" s="1">
         <f>D29*1.25</f>
-        <v>23812.5</v>
+        <v>25062.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:D33" si="10">D29+N$2</f>
-        <v>20050</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" si="10"/>
-        <v>21050</v>
+        <v>21950</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" si="10"/>
-        <v>22050</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" si="10"/>
-        <v>23050</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D34" s="1">
         <f>D33+O$2</f>
-        <v>24150</v>
+        <v>24950</v>
       </c>
       <c r="E34" s="1">
         <f>D34*1.25</f>
-        <v>30187.5</v>
+        <v>31187.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ref="D35:D38" si="12">D34+O$2</f>
-        <v>25250</v>
+        <v>26050</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" si="12"/>
-        <v>26350</v>
+        <v>27150</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" si="12"/>
-        <v>27450</v>
+        <v>28250</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D38" s="1">
         <f t="shared" si="12"/>
-        <v>28550</v>
+        <v>29350</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="D39" s="1">
         <f>D38+P$2</f>
-        <v>29850</v>
+        <v>30650</v>
       </c>
       <c r="E39" s="1">
         <f>D39*1.25</f>
-        <v>37312.5</v>
+        <v>38312.5</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D40" s="1">
         <f t="shared" ref="D40:D44" si="14">D39+P$2</f>
-        <v>31150</v>
+        <v>31950</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" si="14"/>
-        <v>32450</v>
+        <v>33250</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D42" s="1">
         <f t="shared" si="14"/>
-        <v>33750</v>
+        <v>34550</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D43" s="1">
         <f t="shared" si="14"/>
-        <v>35050</v>
+        <v>35850</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D44" s="1">
         <f t="shared" si="14"/>
-        <v>36350</v>
+        <v>37150</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2456B655-3896-491E-AC1E-97E86E20C70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C634C750-5060-4637-9E3A-432E42FEEA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-732" yWindow="4476" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1392,7 +1392,7 @@
         <v>2500</v>
       </c>
       <c r="I2" s="1">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="J2" s="1">
         <v>450</v>
@@ -1485,7 +1485,7 @@
         <v>900</v>
       </c>
       <c r="E5" s="1">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="F5" s="1">
         <v>1500</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D10" s="1">
         <f>I2</f>
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D11" s="1">
         <f>D10+J$2</f>
-        <v>4950</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ref="D12:D14" si="3">D11+J$2</f>
-        <v>5400</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="3"/>
-        <v>5850</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1597,11 +1597,11 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="3"/>
-        <v>6300</v>
+        <v>5800</v>
       </c>
       <c r="E14" s="1">
         <f>D14*1.25</f>
-        <v>7875</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D15" s="1">
         <f>D14+K$2</f>
-        <v>7150</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ref="D16:D19" si="5">D15+K$2</f>
-        <v>8000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="5"/>
-        <v>8850</v>
+        <v>8350</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" si="5"/>
-        <v>9700</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="5"/>
-        <v>10550</v>
+        <v>10050</v>
       </c>
       <c r="E19" s="1">
         <f>D19*1.25</f>
-        <v>13187.5</v>
+        <v>12562.5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="D20" s="1">
         <f>D19+L$2</f>
-        <v>11500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:D24" si="7">D20+L$2</f>
-        <v>12450</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" si="7"/>
-        <v>13400</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" si="7"/>
-        <v>14350</v>
+        <v>13850</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,11 +1775,11 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" si="7"/>
-        <v>15300</v>
+        <v>14800</v>
       </c>
       <c r="E24" s="1">
         <f>D24*1.25</f>
-        <v>19125</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D25" s="1">
         <f>D24+M$2</f>
-        <v>16250</v>
+        <v>15750</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ref="D26:D28" si="8">D25+M$2</f>
-        <v>17200</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" si="8"/>
-        <v>18150</v>
+        <v>17650</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" si="8"/>
-        <v>19100</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1864,11 +1864,11 @@
       </c>
       <c r="D29" s="1">
         <f>D28+N$2</f>
-        <v>20050</v>
+        <v>19550</v>
       </c>
       <c r="E29" s="1">
         <f>D29*1.25</f>
-        <v>25062.5</v>
+        <v>24437.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:D33" si="10">D29+N$2</f>
-        <v>21000</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" si="10"/>
-        <v>21950</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" si="10"/>
-        <v>22900</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" si="10"/>
-        <v>23850</v>
+        <v>23350</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D34" s="1">
         <f>D33+O$2</f>
-        <v>24950</v>
+        <v>24450</v>
       </c>
       <c r="E34" s="1">
         <f>D34*1.25</f>
-        <v>31187.5</v>
+        <v>30562.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ref="D35:D38" si="12">D34+O$2</f>
-        <v>26050</v>
+        <v>25550</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" si="12"/>
-        <v>27150</v>
+        <v>26650</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" si="12"/>
-        <v>28250</v>
+        <v>27750</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D38" s="1">
         <f t="shared" si="12"/>
-        <v>29350</v>
+        <v>28850</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="D39" s="1">
         <f>D38+P$2</f>
-        <v>30650</v>
+        <v>30150</v>
       </c>
       <c r="E39" s="1">
         <f>D39*1.25</f>
-        <v>38312.5</v>
+        <v>37687.5</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D40" s="1">
         <f t="shared" ref="D40:D44" si="14">D39+P$2</f>
-        <v>31950</v>
+        <v>31450</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" si="14"/>
-        <v>33250</v>
+        <v>32750</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D42" s="1">
         <f t="shared" si="14"/>
-        <v>34550</v>
+        <v>34050</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D43" s="1">
         <f t="shared" si="14"/>
-        <v>35850</v>
+        <v>35350</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D44" s="1">
         <f t="shared" si="14"/>
-        <v>37150</v>
+        <v>36650</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C634C750-5060-4637-9E3A-432E42FEEA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DE238B-CDD6-4EC7-96F1-F8E576AFD90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-732" yWindow="4476" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3552" yWindow="1104" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1395,10 +1395,10 @@
         <v>4000</v>
       </c>
       <c r="J2" s="1">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K2" s="1">
-        <v>850</v>
+        <v>750</v>
       </c>
       <c r="L2" s="1">
         <v>950</v>
@@ -1407,13 +1407,13 @@
         <v>950</v>
       </c>
       <c r="N2" s="1">
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="O2" s="1">
         <v>1100</v>
       </c>
       <c r="P2" s="1">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Q2" s="1">
         <v>1.25</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D11" s="1">
         <f>D10+J$2</f>
-        <v>4450</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ref="D12:D14" si="3">D11+J$2</f>
-        <v>4900</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="3"/>
-        <v>5350</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1597,11 +1597,11 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="3"/>
-        <v>5800</v>
+        <v>5600</v>
       </c>
       <c r="E14" s="1">
         <f>D14*1.25</f>
-        <v>7250</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D15" s="1">
         <f>D14+K$2</f>
-        <v>6650</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ref="D16:D19" si="5">D15+K$2</f>
-        <v>7500</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="5"/>
-        <v>8350</v>
+        <v>7850</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" si="5"/>
-        <v>9200</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="5"/>
-        <v>10050</v>
+        <v>9350</v>
       </c>
       <c r="E19" s="1">
         <f>D19*1.25</f>
-        <v>12562.5</v>
+        <v>11687.5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="D20" s="1">
         <f>D19+L$2</f>
-        <v>11000</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:D24" si="7">D20+L$2</f>
-        <v>11950</v>
+        <v>11250</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" si="7"/>
-        <v>12900</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" si="7"/>
-        <v>13850</v>
+        <v>13150</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,11 +1775,11 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" si="7"/>
-        <v>14800</v>
+        <v>14100</v>
       </c>
       <c r="E24" s="1">
         <f>D24*1.25</f>
-        <v>18500</v>
+        <v>17625</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D25" s="1">
         <f>D24+M$2</f>
-        <v>15750</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ref="D26:D28" si="8">D25+M$2</f>
-        <v>16700</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" si="8"/>
-        <v>17650</v>
+        <v>16950</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" si="8"/>
-        <v>18600</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1864,11 +1864,11 @@
       </c>
       <c r="D29" s="1">
         <f>D28+N$2</f>
-        <v>19550</v>
+        <v>18950</v>
       </c>
       <c r="E29" s="1">
         <f>D29*1.25</f>
-        <v>24437.5</v>
+        <v>23687.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:D33" si="10">D29+N$2</f>
-        <v>20500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" si="10"/>
-        <v>21450</v>
+        <v>21050</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" si="10"/>
-        <v>22400</v>
+        <v>22100</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" si="10"/>
-        <v>23350</v>
+        <v>23150</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="D34" s="1">
         <f>D33+O$2</f>
-        <v>24450</v>
+        <v>24250</v>
       </c>
       <c r="E34" s="1">
         <f>D34*1.25</f>
-        <v>30562.5</v>
+        <v>30312.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ref="D35:D38" si="12">D34+O$2</f>
-        <v>25550</v>
+        <v>25350</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" si="12"/>
-        <v>26650</v>
+        <v>26450</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" si="12"/>
-        <v>27750</v>
+        <v>27550</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D38" s="1">
         <f t="shared" si="12"/>
-        <v>28850</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D40" s="1">
         <f t="shared" ref="D40:D44" si="14">D39+P$2</f>
-        <v>31450</v>
+        <v>31650</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" si="14"/>
-        <v>32750</v>
+        <v>33150</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D42" s="1">
         <f t="shared" si="14"/>
-        <v>34050</v>
+        <v>34650</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D43" s="1">
         <f t="shared" si="14"/>
-        <v>35350</v>
+        <v>36150</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D44" s="1">
         <f t="shared" si="14"/>
-        <v>36650</v>
+        <v>37650</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DE238B-CDD6-4EC7-96F1-F8E576AFD90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CD45F7-29E8-4210-9ED4-81599ED829BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3552" yWindow="1104" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1410,10 +1410,10 @@
         <v>1050</v>
       </c>
       <c r="O2" s="1">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="P2" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="Q2" s="1">
         <v>1.25</v>
@@ -1863,12 +1863,12 @@
         <v>19100</v>
       </c>
       <c r="D29" s="1">
-        <f>D28+N$2</f>
-        <v>18950</v>
+        <f>D28+M$2</f>
+        <v>18850</v>
       </c>
       <c r="E29" s="1">
         <f>D29*1.25</f>
-        <v>23687.5</v>
+        <v>23562.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:D33" si="10">D29+N$2</f>
-        <v>20000</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" si="10"/>
-        <v>21050</v>
+        <v>20950</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" si="10"/>
-        <v>22100</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" si="10"/>
-        <v>23150</v>
+        <v>23050</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1952,12 +1952,12 @@
         <v>22450</v>
       </c>
       <c r="D34" s="1">
-        <f>D33+O$2</f>
-        <v>24250</v>
+        <f>D33+N$2</f>
+        <v>24100</v>
       </c>
       <c r="E34" s="1">
         <f>D34*1.25</f>
-        <v>30312.5</v>
+        <v>30125</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ref="D35:D38" si="12">D34+O$2</f>
-        <v>25350</v>
+        <v>25400</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" si="12"/>
-        <v>26450</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" si="12"/>
-        <v>27550</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D38" s="1">
         <f t="shared" si="12"/>
-        <v>28650</v>
+        <v>29300</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2041,12 +2041,12 @@
         <v>29200</v>
       </c>
       <c r="D39" s="1">
-        <f>D38+P$2</f>
-        <v>30150</v>
+        <f>D38+O$2</f>
+        <v>30600</v>
       </c>
       <c r="E39" s="1">
         <f>D39*1.25</f>
-        <v>37687.5</v>
+        <v>38250</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D40" s="1">
         <f t="shared" ref="D40:D44" si="14">D39+P$2</f>
-        <v>31650</v>
+        <v>32600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" si="14"/>
-        <v>33150</v>
+        <v>34600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D42" s="1">
         <f t="shared" si="14"/>
-        <v>34650</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D43" s="1">
         <f t="shared" si="14"/>
-        <v>36150</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D44" s="1">
         <f t="shared" si="14"/>
-        <v>37650</v>
+        <v>40600</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CD45F7-29E8-4210-9ED4-81599ED829BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D66F7C-7079-454C-A796-AB30ECBB129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2676" yWindow="3060" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1297,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90AC4D0A-3569-4D64-9EA4-6DBEB5A45CA9}">
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -1413,7 +1413,7 @@
         <v>1300</v>
       </c>
       <c r="P2" s="1">
-        <v>2000</v>
+        <v>1450</v>
       </c>
       <c r="Q2" s="1">
         <v>1.25</v>
@@ -1491,10 +1491,10 @@
         <v>1500</v>
       </c>
       <c r="G5" s="1">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="H5" s="1">
-        <v>1500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2062,8 +2062,8 @@
         <v>30750</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" ref="D40:D44" si="14">D39+P$2</f>
-        <v>32600</v>
+        <f t="shared" ref="D40:D47" si="14">D39+P$2</f>
+        <v>32050</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" si="14"/>
-        <v>34600</v>
+        <v>33500</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D42" s="1">
         <f t="shared" si="14"/>
-        <v>36600</v>
+        <v>34950</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D43" s="1">
         <f t="shared" si="14"/>
-        <v>38600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2131,34 @@
       </c>
       <c r="D44" s="1">
         <f t="shared" si="14"/>
-        <v>40600</v>
+        <v>37850</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>36</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="14"/>
+        <v>39300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>37</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="14"/>
+        <v>40750</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>38</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="14"/>
+        <v>42200</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D66F7C-7079-454C-A796-AB30ECBB129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1B3E1F-C935-4931-8583-79A0955877A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2676" yWindow="3060" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
   <si>
     <t>玩家初始分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,6 +124,10 @@
   </si>
   <si>
     <t>x2点位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家高分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1401,19 +1405,19 @@
         <v>750</v>
       </c>
       <c r="L2" s="1">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="M2" s="1">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="N2" s="1">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="O2" s="1">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="P2" s="1">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="Q2" s="1">
         <v>1.25</v>
@@ -1513,6 +1517,9 @@
       <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1531,6 +1538,10 @@
         <v>4000</v>
       </c>
       <c r="E10" s="4"/>
+      <c r="F10" s="1">
+        <f>A2</f>
+        <v>5000</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1548,6 +1559,10 @@
         <f>D10+J$2</f>
         <v>4400</v>
       </c>
+      <c r="F11" s="1">
+        <f>F10+B$4</f>
+        <v>5700</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1565,6 +1580,10 @@
         <f t="shared" ref="D12:D14" si="3">D11+J$2</f>
         <v>4800</v>
       </c>
+      <c r="F12" s="1">
+        <f t="shared" ref="F12:F44" si="4">F11+B$4</f>
+        <v>6400</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1582,6 +1601,10 @@
         <f t="shared" si="3"/>
         <v>5200</v>
       </c>
+      <c r="F13" s="1">
+        <f t="shared" si="4"/>
+        <v>7100</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1603,6 +1626,10 @@
         <f>D14*1.25</f>
         <v>7000</v>
       </c>
+      <c r="F14" s="1">
+        <f t="shared" si="4"/>
+        <v>7800</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1620,6 +1647,10 @@
         <f>D14+K$2</f>
         <v>6350</v>
       </c>
+      <c r="F15" s="1">
+        <f>F14+C$4</f>
+        <v>8800</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1630,15 +1661,19 @@
         <v>11</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" ref="C16:C19" si="4">C15+C$2</f>
+        <f t="shared" ref="C16:C19" si="5">C15+C$2</f>
         <v>8300</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16:D19" si="5">D15+K$2</f>
+        <f t="shared" ref="D16:D19" si="6">D15+K$2</f>
         <v>7100</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="1">
+        <f t="shared" ref="F16:F44" si="7">F15+C$4</f>
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>8</v>
       </c>
@@ -1647,15 +1682,19 @@
         <v>12</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8950</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7850</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="1">
+        <f t="shared" si="7"/>
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>9</v>
       </c>
@@ -1664,15 +1703,19 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9600</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8600</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="1">
+        <f t="shared" si="7"/>
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>10</v>
       </c>
@@ -1681,19 +1724,23 @@
         <v>14</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10250</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9350</v>
       </c>
       <c r="E19" s="1">
         <f>D19*1.25</f>
         <v>11687.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="1">
+        <f t="shared" si="7"/>
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>11</v>
       </c>
@@ -1707,10 +1754,14 @@
       </c>
       <c r="D20" s="1">
         <f>D19+L$2</f>
-        <v>10300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10350</v>
+      </c>
+      <c r="F20" s="1">
+        <f>F19+D$4</f>
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>12</v>
       </c>
@@ -1719,15 +1770,19 @@
         <v>16</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" ref="C21:C24" si="6">C20+D$2</f>
+        <f t="shared" ref="C21:C24" si="8">C20+D$2</f>
         <v>12150</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ref="D21:D24" si="7">D20+L$2</f>
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D21:D24" si="9">D20+L$2</f>
+        <v>11350</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" ref="F21:F44" si="10">F20+D$4</f>
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>13</v>
       </c>
@@ -1736,15 +1791,19 @@
         <v>17</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>13100</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="7"/>
-        <v>12200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>12350</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="10"/>
+        <v>16400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>14</v>
       </c>
@@ -1753,15 +1812,19 @@
         <v>18</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>14050</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="7"/>
-        <v>13150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>13350</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="10"/>
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>15</v>
       </c>
@@ -1770,19 +1833,23 @@
         <v>19</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>15000</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="7"/>
-        <v>14100</v>
+        <f t="shared" si="9"/>
+        <v>14350</v>
       </c>
       <c r="E24" s="1">
         <f>D24*1.25</f>
-        <v>17625</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17937.5</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="10"/>
+        <v>18800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>16</v>
       </c>
@@ -1796,10 +1863,14 @@
       </c>
       <c r="D25" s="1">
         <f>D24+M$2</f>
-        <v>15050</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15450</v>
+      </c>
+      <c r="F25" s="1">
+        <f>F24+E$4-B$4</f>
+        <v>19600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>17</v>
       </c>
@@ -1812,11 +1883,15 @@
         <v>16500</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26:D28" si="8">D25+M$2</f>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D26:D28" si="11">D25+M$2</f>
+        <v>16550</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" ref="F26:F44" si="12">F25+E$4-B$4</f>
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>18</v>
       </c>
@@ -1825,15 +1900,19 @@
         <v>20</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" ref="C27:C28" si="9">C26+E$2-B$2</f>
+        <f t="shared" ref="C27:C28" si="13">C26+E$2-B$2</f>
         <v>17250</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="8"/>
-        <v>16950</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>17650</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="12"/>
+        <v>21200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>19</v>
       </c>
@@ -1842,15 +1921,19 @@
         <v>20</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>18000</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="8"/>
-        <v>17900</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>18750</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="12"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>20</v>
       </c>
@@ -1859,19 +1942,23 @@
         <v>20</v>
       </c>
       <c r="C29" s="1">
-        <f>C28+F$2-B$2</f>
-        <v>19100</v>
+        <f>C28+E$2-B$2</f>
+        <v>18750</v>
       </c>
       <c r="D29" s="1">
         <f>D28+M$2</f>
-        <v>18850</v>
+        <v>19850</v>
       </c>
       <c r="E29" s="1">
         <f>D29*1.25</f>
-        <v>23562.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>24812.5</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="12"/>
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>21</v>
       </c>
@@ -1881,14 +1968,18 @@
       </c>
       <c r="C30" s="1">
         <f>C29+F$2-C$2</f>
-        <v>20050</v>
+        <v>19700</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" ref="D30:D33" si="10">D29+N$2</f>
-        <v>19900</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D30:D33" si="14">D29+N$2</f>
+        <v>21050</v>
+      </c>
+      <c r="F30" s="1">
+        <f>F29+F$4-C$4</f>
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>22</v>
       </c>
@@ -1897,15 +1988,19 @@
         <v>20</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" ref="C31:C34" si="11">C30+E$2-C$2</f>
+        <f t="shared" ref="C31:C34" si="15">C30+F$2-C$2</f>
         <v>20650</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="10"/>
-        <v>20950</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>22250</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" ref="F31:F44" si="16">F30+F$4-C$4</f>
+        <v>24800</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>23</v>
       </c>
@@ -1914,15 +2009,19 @@
         <v>20</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="11"/>
-        <v>21250</v>
+        <f t="shared" si="15"/>
+        <v>21600</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="10"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>23450</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="16"/>
+        <v>25800</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24</v>
       </c>
@@ -1931,15 +2030,19 @@
         <v>20</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="11"/>
-        <v>21850</v>
+        <f t="shared" si="15"/>
+        <v>22550</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="10"/>
-        <v>23050</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>24650</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="16"/>
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>25</v>
       </c>
@@ -1948,19 +2051,23 @@
         <v>20</v>
       </c>
       <c r="C34" s="1">
-        <f t="shared" si="11"/>
-        <v>22450</v>
+        <f t="shared" si="15"/>
+        <v>23500</v>
       </c>
       <c r="D34" s="1">
         <f>D33+N$2</f>
-        <v>24100</v>
+        <v>25850</v>
       </c>
       <c r="E34" s="1">
         <f>D34*1.25</f>
-        <v>30125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32312.5</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="16"/>
+        <v>27800</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>26</v>
       </c>
@@ -1969,15 +2076,19 @@
         <v>20</v>
       </c>
       <c r="C35" s="1">
-        <f>C34+G$2-C$2</f>
-        <v>23800</v>
+        <f>C34+G$2-D$2</f>
+        <v>24550</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35:D38" si="12">D34+O$2</f>
-        <v>25400</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D35:D38" si="17">D34+O$2</f>
+        <v>27200</v>
+      </c>
+      <c r="F35" s="1">
+        <f>F34+G$4-D$4</f>
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>27</v>
       </c>
@@ -1986,15 +2097,19 @@
         <v>20</v>
       </c>
       <c r="C36" s="1">
-        <f t="shared" ref="C36:C39" si="13">C35+G$2-C$2</f>
-        <v>25150</v>
+        <f t="shared" ref="C36:C44" si="18">C35+G$2-D$2</f>
+        <v>25600</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="12"/>
-        <v>26700</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>28550</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" ref="F36:F44" si="19">F35+G$4-D$4</f>
+        <v>30400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>28</v>
       </c>
@@ -2003,15 +2118,19 @@
         <v>20</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" si="13"/>
-        <v>26500</v>
+        <f t="shared" si="18"/>
+        <v>26650</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="12"/>
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>29900</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="19"/>
+        <v>31700</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>29</v>
       </c>
@@ -2020,15 +2139,19 @@
         <v>20</v>
       </c>
       <c r="C38" s="1">
-        <f t="shared" si="13"/>
-        <v>27850</v>
+        <f t="shared" si="18"/>
+        <v>27700</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="12"/>
-        <v>29300</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>31250</v>
+      </c>
+      <c r="F38" s="1">
+        <f t="shared" si="19"/>
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>30</v>
       </c>
@@ -2037,19 +2160,23 @@
         <v>20</v>
       </c>
       <c r="C39" s="1">
-        <f t="shared" si="13"/>
-        <v>29200</v>
+        <f t="shared" si="18"/>
+        <v>28750</v>
       </c>
       <c r="D39" s="1">
         <f>D38+O$2</f>
-        <v>30600</v>
+        <v>32600</v>
       </c>
       <c r="E39" s="1">
         <f>D39*1.25</f>
-        <v>38250</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40750</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" si="19"/>
+        <v>34300</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>31</v>
       </c>
@@ -2058,15 +2185,19 @@
         <v>20</v>
       </c>
       <c r="C40" s="1">
-        <f>C39+H$2-D$2</f>
-        <v>30750</v>
+        <f>C39+H$2-E$2</f>
+        <v>30000</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" ref="D40:D47" si="14">D39+P$2</f>
-        <v>32050</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D40:D47" si="20">D39+P$2</f>
+        <v>34000</v>
+      </c>
+      <c r="F40" s="1">
+        <f>F39+H$4-E$4</f>
+        <v>35800</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>32</v>
       </c>
@@ -2075,15 +2206,19 @@
         <v>20</v>
       </c>
       <c r="C41" s="1">
-        <f t="shared" ref="C41:C44" si="15">C40+H$2-D$2</f>
-        <v>32300</v>
+        <f t="shared" ref="C41:C44" si="21">C40+H$2-E$2</f>
+        <v>31250</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="14"/>
-        <v>33500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>35400</v>
+      </c>
+      <c r="F41" s="1">
+        <f t="shared" ref="F41:F44" si="22">F40+H$4-E$4</f>
+        <v>37300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>33</v>
       </c>
@@ -2092,15 +2227,19 @@
         <v>20</v>
       </c>
       <c r="C42" s="1">
-        <f t="shared" si="15"/>
-        <v>33850</v>
+        <f t="shared" si="21"/>
+        <v>32500</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="14"/>
-        <v>34950</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>36800</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" si="22"/>
+        <v>38800</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>34</v>
       </c>
@@ -2109,15 +2248,19 @@
         <v>20</v>
       </c>
       <c r="C43" s="1">
-        <f t="shared" si="15"/>
-        <v>35400</v>
+        <f t="shared" si="21"/>
+        <v>33750</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="14"/>
-        <v>36400</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>38200</v>
+      </c>
+      <c r="F43" s="1">
+        <f t="shared" si="22"/>
+        <v>40300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>35</v>
       </c>
@@ -2126,39 +2269,43 @@
         <v>20</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" si="15"/>
-        <v>36950</v>
+        <f t="shared" si="21"/>
+        <v>35000</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="14"/>
-        <v>37850</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>39600</v>
+      </c>
+      <c r="F44" s="1">
+        <f t="shared" si="22"/>
+        <v>41800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>36</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="14"/>
-        <v>39300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>37</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="14"/>
-        <v>40750</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>42400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>38</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="14"/>
-        <v>42200</v>
+        <f t="shared" si="20"/>
+        <v>43800</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1B3E1F-C935-4931-8583-79A0955877A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590AAC52-8BB6-4529-ABA1-67DC5C9408FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2400" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
   <si>
     <t>玩家初始分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,6 +128,14 @@
   </si>
   <si>
     <t>玩家高分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家初始分4500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调权</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1313,7 +1321,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>7</v>
@@ -1366,7 +1374,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="B2" s="1">
         <f>(B3+B4)/2</f>
@@ -1396,31 +1404,32 @@
         <v>2500</v>
       </c>
       <c r="I2" s="1">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="J2" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K2" s="1">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="L2" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="M2" s="1">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="N2" s="1">
         <v>1200</v>
       </c>
       <c r="O2" s="1">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="P2" s="1">
         <v>1400</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.25</v>
+        <f>I3</f>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -1448,6 +1457,9 @@
       <c r="H3" s="1">
         <v>1500</v>
       </c>
+      <c r="I3" s="1">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1520,6 +1532,9 @@
       <c r="F9" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="H9" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1530,17 +1545,25 @@
         <v>5</v>
       </c>
       <c r="C10" s="1">
-        <f>A2</f>
+        <f>A2+B2</f>
         <v>5000</v>
       </c>
       <c r="D10" s="1">
-        <f>I2</f>
-        <v>4000</v>
+        <f>I2+J2</f>
+        <v>4800</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1">
-        <f>A2</f>
-        <v>5000</v>
+        <f>A2+B4</f>
+        <v>5200</v>
+      </c>
+      <c r="H10" s="1">
+        <f>$I$2+0.8*(D10-$I$2)</f>
+        <v>4700</v>
+      </c>
+      <c r="I10" s="1">
+        <f>$I$2+1.25*(D10-$I$2)</f>
+        <v>4925</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1557,11 +1580,19 @@
       </c>
       <c r="D11" s="1">
         <f>D10+J$2</f>
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="F11" s="1">
         <f>F10+B$4</f>
-        <v>5700</v>
+        <v>5900</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" ref="H11:H44" si="1">$I$2+0.8*(D11-$I$2)</f>
+        <v>5100</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" ref="I11:I44" si="2">$I$2+1.25*(D11-$I$2)</f>
+        <v>5550</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1569,20 +1600,28 @@
         <v>3</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" ref="B12:B25" si="1">B11+1</f>
+        <f t="shared" ref="B12:B25" si="3">B11+1</f>
         <v>7</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" ref="C12:C14" si="2">C11+B$2</f>
+        <f t="shared" ref="C12:C14" si="4">C11+B$2</f>
         <v>6000</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" ref="D12:D14" si="3">D11+J$2</f>
-        <v>4800</v>
+        <f t="shared" ref="D12:D14" si="5">D11+J$2</f>
+        <v>5800</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" ref="F12:F44" si="4">F11+B$4</f>
-        <v>6400</v>
+        <f t="shared" ref="F12:F14" si="6">F11+B$4</f>
+        <v>6600</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>5500</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="2"/>
+        <v>6175</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1590,20 +1629,28 @@
         <v>4</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6500</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="3"/>
-        <v>5200</v>
+        <f t="shared" si="5"/>
+        <v>6300</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="4"/>
-        <v>7100</v>
+        <f t="shared" si="6"/>
+        <v>7300</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>5900</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="2"/>
+        <v>6800</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1611,24 +1658,32 @@
         <v>5</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="3"/>
-        <v>5600</v>
+        <f t="shared" si="5"/>
+        <v>6800</v>
       </c>
       <c r="E14" s="1">
-        <f>D14*1.25</f>
-        <v>7000</v>
+        <f>D14*$I$3</f>
+        <v>9520</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="4"/>
-        <v>7800</v>
+        <f t="shared" si="6"/>
+        <v>8000</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>6300</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="2"/>
+        <v>7425</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1636,7 +1691,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="C15" s="1">
@@ -1645,11 +1700,19 @@
       </c>
       <c r="D15" s="1">
         <f>D14+K$2</f>
-        <v>6350</v>
+        <v>7650</v>
       </c>
       <c r="F15" s="1">
         <f>F14+C$4</f>
-        <v>8800</v>
+        <v>9000</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>6980</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="2"/>
+        <v>8487.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1657,95 +1720,127 @@
         <v>7</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" ref="C16:C19" si="5">C15+C$2</f>
+        <f t="shared" ref="C16:C19" si="7">C15+C$2</f>
         <v>8300</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16:D19" si="6">D15+K$2</f>
-        <v>7100</v>
+        <f t="shared" ref="D16:D19" si="8">D15+K$2</f>
+        <v>8500</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" ref="F16:F44" si="7">F15+C$4</f>
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F16:F19" si="9">F15+C$4</f>
+        <v>10000</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>7660</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="2"/>
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>8</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>8950</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="6"/>
-        <v>7850</v>
+        <f t="shared" si="8"/>
+        <v>9350</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="7"/>
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>11000</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>8340</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="2"/>
+        <v>10612.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>9</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9600</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="6"/>
-        <v>8600</v>
+        <f t="shared" si="8"/>
+        <v>10200</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="7"/>
-        <v>11800</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>12000</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>9020</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="2"/>
+        <v>11675</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>10</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>10250</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="6"/>
-        <v>9350</v>
+        <f t="shared" si="8"/>
+        <v>11050</v>
       </c>
       <c r="E19" s="1">
-        <f>D19*1.25</f>
-        <v>11687.5</v>
+        <f>D19*$I$3</f>
+        <v>15469.999999999998</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="7"/>
-        <v>12800</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>13000</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
+        <v>9700</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="2"/>
+        <v>12737.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>11</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="C20" s="1">
@@ -1754,14 +1849,22 @@
       </c>
       <c r="D20" s="1">
         <f>D19+L$2</f>
-        <v>10350</v>
+        <v>12150</v>
       </c>
       <c r="F20" s="1">
         <f>F19+D$4</f>
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14200</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
+        <v>10580</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="2"/>
+        <v>14112.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>12</v>
       </c>
@@ -1770,91 +1873,123 @@
         <v>16</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" ref="C21:C24" si="8">C20+D$2</f>
+        <f t="shared" ref="C21:C24" si="10">C20+D$2</f>
         <v>12150</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ref="D21:D24" si="9">D20+L$2</f>
-        <v>11350</v>
+        <f t="shared" ref="D21:D24" si="11">D20+L$2</f>
+        <v>13250</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" ref="F21:F44" si="10">F20+D$4</f>
-        <v>15200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F21:F24" si="12">F20+D$4</f>
+        <v>15400</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="1"/>
+        <v>11460</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="2"/>
+        <v>15487.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>13</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13100</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="9"/>
-        <v>12350</v>
+        <f t="shared" si="11"/>
+        <v>14350</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="10"/>
-        <v>16400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>16600</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="1"/>
+        <v>12340</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="2"/>
+        <v>16862.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>14</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14050</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="9"/>
-        <v>13350</v>
+        <f t="shared" si="11"/>
+        <v>15450</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="10"/>
-        <v>17600</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>17800</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="1"/>
+        <v>13220</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="2"/>
+        <v>18237.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>15</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>15000</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="9"/>
-        <v>14350</v>
+        <f t="shared" si="11"/>
+        <v>16550</v>
       </c>
       <c r="E24" s="1">
-        <f>D24*1.25</f>
-        <v>17937.5</v>
+        <f>D24*$I$3</f>
+        <v>23170</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="10"/>
-        <v>18800</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>19000</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="1"/>
+        <v>14100</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="2"/>
+        <v>19612.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>16</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="C25" s="1">
@@ -1863,14 +1998,22 @@
       </c>
       <c r="D25" s="1">
         <f>D24+M$2</f>
-        <v>15450</v>
+        <v>17750</v>
       </c>
       <c r="F25" s="1">
         <f>F24+E$4-B$4</f>
-        <v>19600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19800</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="1"/>
+        <v>15060</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="2"/>
+        <v>21112.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>17</v>
       </c>
@@ -1883,15 +2026,23 @@
         <v>16500</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26:D28" si="11">D25+M$2</f>
-        <v>16550</v>
+        <f t="shared" ref="D26:D28" si="13">D25+M$2</f>
+        <v>18950</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" ref="F26:F44" si="12">F25+E$4-B$4</f>
-        <v>20400</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F26:F29" si="14">F25+E$4-B$4</f>
+        <v>20600</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>16020</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="2"/>
+        <v>22612.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>18</v>
       </c>
@@ -1900,19 +2051,27 @@
         <v>20</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" ref="C27:C28" si="13">C26+E$2-B$2</f>
+        <f t="shared" ref="C27:C28" si="15">C26+E$2-B$2</f>
         <v>17250</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="11"/>
-        <v>17650</v>
+        <f t="shared" si="13"/>
+        <v>20150</v>
       </c>
       <c r="F27" s="1">
-        <f t="shared" si="12"/>
-        <v>21200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>21400</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="1"/>
+        <v>16980</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="2"/>
+        <v>24112.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>19</v>
       </c>
@@ -1921,19 +2080,27 @@
         <v>20</v>
       </c>
       <c r="C28" s="1">
+        <f t="shared" si="15"/>
+        <v>18000</v>
+      </c>
+      <c r="D28" s="1">
         <f t="shared" si="13"/>
-        <v>18000</v>
-      </c>
-      <c r="D28" s="1">
-        <f t="shared" si="11"/>
-        <v>18750</v>
+        <v>21350</v>
       </c>
       <c r="F28" s="1">
-        <f t="shared" si="12"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>22200</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="1"/>
+        <v>17940</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="2"/>
+        <v>25612.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>20</v>
       </c>
@@ -1947,18 +2114,26 @@
       </c>
       <c r="D29" s="1">
         <f>D28+M$2</f>
-        <v>19850</v>
+        <v>22550</v>
       </c>
       <c r="E29" s="1">
-        <f>D29*1.25</f>
-        <v>24812.5</v>
+        <f>D29*$I$3</f>
+        <v>31569.999999999996</v>
       </c>
       <c r="F29" s="1">
-        <f t="shared" si="12"/>
-        <v>22800</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>23000</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="1"/>
+        <v>18900</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="2"/>
+        <v>27112.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>21</v>
       </c>
@@ -1971,15 +2146,23 @@
         <v>19700</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" ref="D30:D33" si="14">D29+N$2</f>
-        <v>21050</v>
+        <f t="shared" ref="D30:D33" si="16">D29+N$2</f>
+        <v>23750</v>
       </c>
       <c r="F30" s="1">
         <f>F29+F$4-C$4</f>
-        <v>23800</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>24000</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
+        <v>19860</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="2"/>
+        <v>28612.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>22</v>
       </c>
@@ -1988,19 +2171,27 @@
         <v>20</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" ref="C31:C34" si="15">C30+F$2-C$2</f>
+        <f t="shared" ref="C31:C34" si="17">C30+F$2-C$2</f>
         <v>20650</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="14"/>
-        <v>22250</v>
+        <f t="shared" si="16"/>
+        <v>24950</v>
       </c>
       <c r="F31" s="1">
-        <f t="shared" ref="F31:F44" si="16">F30+F$4-C$4</f>
-        <v>24800</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F31:F34" si="18">F30+F$4-C$4</f>
+        <v>25000</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="1"/>
+        <v>20820</v>
+      </c>
+      <c r="I31" s="1">
+        <f t="shared" si="2"/>
+        <v>30112.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>23</v>
       </c>
@@ -2009,19 +2200,27 @@
         <v>20</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>21600</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="14"/>
-        <v>23450</v>
+        <f t="shared" si="16"/>
+        <v>26150</v>
       </c>
       <c r="F32" s="1">
-        <f t="shared" si="16"/>
-        <v>25800</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>26000</v>
+      </c>
+      <c r="H32" s="1">
+        <f t="shared" si="1"/>
+        <v>21780</v>
+      </c>
+      <c r="I32" s="1">
+        <f t="shared" si="2"/>
+        <v>31612.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24</v>
       </c>
@@ -2030,19 +2229,27 @@
         <v>20</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>22550</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="14"/>
-        <v>24650</v>
+        <f t="shared" si="16"/>
+        <v>27350</v>
       </c>
       <c r="F33" s="1">
-        <f t="shared" si="16"/>
-        <v>26800</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>27000</v>
+      </c>
+      <c r="H33" s="1">
+        <f t="shared" si="1"/>
+        <v>22740</v>
+      </c>
+      <c r="I33" s="1">
+        <f t="shared" si="2"/>
+        <v>33112.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>25</v>
       </c>
@@ -2051,23 +2258,31 @@
         <v>20</v>
       </c>
       <c r="C34" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>23500</v>
       </c>
       <c r="D34" s="1">
         <f>D33+N$2</f>
-        <v>25850</v>
+        <v>28550</v>
       </c>
       <c r="E34" s="1">
-        <f>D34*1.25</f>
-        <v>32312.5</v>
+        <f>D34*$I$3</f>
+        <v>39970</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="16"/>
-        <v>27800</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>28000</v>
+      </c>
+      <c r="H34" s="1">
+        <f t="shared" si="1"/>
+        <v>23700</v>
+      </c>
+      <c r="I34" s="1">
+        <f t="shared" si="2"/>
+        <v>34612.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>26</v>
       </c>
@@ -2080,15 +2295,23 @@
         <v>24550</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35:D38" si="17">D34+O$2</f>
-        <v>27200</v>
+        <f t="shared" ref="D35:D38" si="19">D34+O$2</f>
+        <v>29750</v>
       </c>
       <c r="F35" s="1">
         <f>F34+G$4-D$4</f>
-        <v>29100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29300</v>
+      </c>
+      <c r="H35" s="1">
+        <f t="shared" si="1"/>
+        <v>24660</v>
+      </c>
+      <c r="I35" s="1">
+        <f t="shared" si="2"/>
+        <v>36112.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>27</v>
       </c>
@@ -2097,19 +2320,27 @@
         <v>20</v>
       </c>
       <c r="C36" s="1">
-        <f t="shared" ref="C36:C44" si="18">C35+G$2-D$2</f>
+        <f t="shared" ref="C36:C39" si="20">C35+G$2-D$2</f>
         <v>25600</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="17"/>
-        <v>28550</v>
+        <f t="shared" si="19"/>
+        <v>30950</v>
       </c>
       <c r="F36" s="1">
-        <f t="shared" ref="F36:F44" si="19">F35+G$4-D$4</f>
-        <v>30400</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F36:F39" si="21">F35+G$4-D$4</f>
+        <v>30600</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="1"/>
+        <v>25620</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="2"/>
+        <v>37612.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>28</v>
       </c>
@@ -2118,19 +2349,27 @@
         <v>20</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>26650</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="17"/>
-        <v>29900</v>
+        <f t="shared" si="19"/>
+        <v>32150</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="19"/>
-        <v>31700</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="21"/>
+        <v>31900</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="1"/>
+        <v>26580</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="2"/>
+        <v>39112.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>29</v>
       </c>
@@ -2139,19 +2378,27 @@
         <v>20</v>
       </c>
       <c r="C38" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>27700</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="17"/>
-        <v>31250</v>
+        <f t="shared" si="19"/>
+        <v>33350</v>
       </c>
       <c r="F38" s="1">
-        <f t="shared" si="19"/>
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="21"/>
+        <v>33200</v>
+      </c>
+      <c r="H38" s="1">
+        <f t="shared" si="1"/>
+        <v>27540</v>
+      </c>
+      <c r="I38" s="1">
+        <f t="shared" si="2"/>
+        <v>40612.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>30</v>
       </c>
@@ -2160,23 +2407,31 @@
         <v>20</v>
       </c>
       <c r="C39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>28750</v>
       </c>
       <c r="D39" s="1">
         <f>D38+O$2</f>
-        <v>32600</v>
+        <v>34550</v>
       </c>
       <c r="E39" s="1">
-        <f>D39*1.25</f>
-        <v>40750</v>
+        <f>D39*$I$3</f>
+        <v>48370</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="19"/>
-        <v>34300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="21"/>
+        <v>34500</v>
+      </c>
+      <c r="H39" s="1">
+        <f t="shared" si="1"/>
+        <v>28500</v>
+      </c>
+      <c r="I39" s="1">
+        <f t="shared" si="2"/>
+        <v>42112.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>31</v>
       </c>
@@ -2189,15 +2444,23 @@
         <v>30000</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" ref="D40:D47" si="20">D39+P$2</f>
-        <v>34000</v>
+        <f t="shared" ref="D40:D47" si="22">D39+P$2</f>
+        <v>35950</v>
       </c>
       <c r="F40" s="1">
         <f>F39+H$4-E$4</f>
-        <v>35800</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36000</v>
+      </c>
+      <c r="H40" s="1">
+        <f t="shared" si="1"/>
+        <v>29620</v>
+      </c>
+      <c r="I40" s="1">
+        <f t="shared" si="2"/>
+        <v>43862.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>32</v>
       </c>
@@ -2206,19 +2469,27 @@
         <v>20</v>
       </c>
       <c r="C41" s="1">
-        <f t="shared" ref="C41:C44" si="21">C40+H$2-E$2</f>
+        <f t="shared" ref="C41:C44" si="23">C40+H$2-E$2</f>
         <v>31250</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="20"/>
-        <v>35400</v>
+        <f t="shared" si="22"/>
+        <v>37350</v>
       </c>
       <c r="F41" s="1">
-        <f t="shared" ref="F41:F44" si="22">F40+H$4-E$4</f>
-        <v>37300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F41:F44" si="24">F40+H$4-E$4</f>
+        <v>37500</v>
+      </c>
+      <c r="H41" s="1">
+        <f t="shared" si="1"/>
+        <v>30740</v>
+      </c>
+      <c r="I41" s="1">
+        <f t="shared" si="2"/>
+        <v>45612.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>33</v>
       </c>
@@ -2227,19 +2498,27 @@
         <v>20</v>
       </c>
       <c r="C42" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>32500</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="20"/>
-        <v>36800</v>
+        <f t="shared" si="22"/>
+        <v>38750</v>
       </c>
       <c r="F42" s="1">
-        <f t="shared" si="22"/>
-        <v>38800</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="24"/>
+        <v>39000</v>
+      </c>
+      <c r="H42" s="1">
+        <f t="shared" si="1"/>
+        <v>31860</v>
+      </c>
+      <c r="I42" s="1">
+        <f t="shared" si="2"/>
+        <v>47362.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>34</v>
       </c>
@@ -2248,19 +2527,27 @@
         <v>20</v>
       </c>
       <c r="C43" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>33750</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="20"/>
-        <v>38200</v>
+        <f t="shared" si="22"/>
+        <v>40150</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" si="22"/>
-        <v>40300</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="24"/>
+        <v>40500</v>
+      </c>
+      <c r="H43" s="1">
+        <f t="shared" si="1"/>
+        <v>32980</v>
+      </c>
+      <c r="I43" s="1">
+        <f t="shared" si="2"/>
+        <v>49112.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>35</v>
       </c>
@@ -2269,43 +2556,51 @@
         <v>20</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>35000</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="20"/>
-        <v>39600</v>
+        <f t="shared" si="22"/>
+        <v>41550</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" si="22"/>
-        <v>41800</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="24"/>
+        <v>42000</v>
+      </c>
+      <c r="H44" s="1">
+        <f t="shared" si="1"/>
+        <v>34100</v>
+      </c>
+      <c r="I44" s="1">
+        <f t="shared" si="2"/>
+        <v>50862.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>36</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="20"/>
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>42950</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>37</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="20"/>
-        <v>42400</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>44350</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>38</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="20"/>
-        <v>43800</v>
+        <f t="shared" si="22"/>
+        <v>45750</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590AAC52-8BB6-4529-ABA1-67DC5C9408FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5769DA90-DFE4-4391-B176-B84BFCE3FDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1404,7 +1404,7 @@
         <v>2500</v>
       </c>
       <c r="I2" s="1">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="J2" s="1">
         <v>500</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D10" s="1">
         <f>I2+J2</f>
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1">
@@ -1559,11 +1559,11 @@
       </c>
       <c r="H10" s="1">
         <f>$I$2+0.8*(D10-$I$2)</f>
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="I10" s="1">
         <f>$I$2+1.25*(D10-$I$2)</f>
-        <v>4925</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D11" s="1">
         <f>D10+J$2</f>
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="F11" s="1">
         <f>F10+B$4</f>
@@ -1588,11 +1588,11 @@
       </c>
       <c r="H11" s="1">
         <f t="shared" ref="H11:H44" si="1">$I$2+0.8*(D11-$I$2)</f>
-        <v>5100</v>
+        <v>5300</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ref="I11:I44" si="2">$I$2+1.25*(D11-$I$2)</f>
-        <v>5550</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ref="D12:D14" si="5">D11+J$2</f>
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" ref="F12:F14" si="6">F11+B$4</f>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" si="1"/>
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="2"/>
-        <v>6175</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="5"/>
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" si="6"/>
@@ -1646,11 +1646,11 @@
       </c>
       <c r="H13" s="1">
         <f t="shared" si="1"/>
-        <v>5900</v>
+        <v>6100</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="2"/>
-        <v>6800</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="5"/>
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="E14" s="1">
         <f>D14*$I$3</f>
-        <v>9520</v>
+        <v>9800</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="6"/>
@@ -1679,11 +1679,11 @@
       </c>
       <c r="H14" s="1">
         <f t="shared" si="1"/>
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>7425</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D15" s="1">
         <f>D14+K$2</f>
-        <v>7650</v>
+        <v>7850</v>
       </c>
       <c r="F15" s="1">
         <f>F14+C$4</f>
@@ -1708,11 +1708,11 @@
       </c>
       <c r="H15" s="1">
         <f t="shared" si="1"/>
-        <v>6980</v>
+        <v>7180</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="2"/>
-        <v>8487.5</v>
+        <v>8687.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ref="D16:D19" si="8">D15+K$2</f>
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" ref="F16:F19" si="9">F15+C$4</f>
@@ -1737,11 +1737,11 @@
       </c>
       <c r="H16" s="1">
         <f t="shared" si="1"/>
-        <v>7660</v>
+        <v>7860</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="2"/>
-        <v>9550</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="8"/>
-        <v>9350</v>
+        <v>9550</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="9"/>
@@ -1766,11 +1766,11 @@
       </c>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
-        <v>8340</v>
+        <v>8540</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>10612.5</v>
+        <v>10812.5</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" si="8"/>
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="9"/>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>9020</v>
+        <v>9220</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="2"/>
-        <v>11675</v>
+        <v>11875</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="8"/>
-        <v>11050</v>
+        <v>11250</v>
       </c>
       <c r="E19" s="1">
         <f>D19*$I$3</f>
-        <v>15469.999999999998</v>
+        <v>15749.999999999998</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="9"/>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
-        <v>9700</v>
+        <v>9900</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="2"/>
-        <v>12737.5</v>
+        <v>12937.5</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D20" s="1">
         <f>D19+L$2</f>
-        <v>12150</v>
+        <v>12350</v>
       </c>
       <c r="F20" s="1">
         <f>F19+D$4</f>
@@ -1857,11 +1857,11 @@
       </c>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
-        <v>10580</v>
+        <v>10780</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="2"/>
-        <v>14112.5</v>
+        <v>14312.5</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:D24" si="11">D20+L$2</f>
-        <v>13250</v>
+        <v>13450</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" ref="F21:F24" si="12">F20+D$4</f>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="H21" s="1">
         <f t="shared" si="1"/>
-        <v>11460</v>
+        <v>11660</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="2"/>
-        <v>15487.5</v>
+        <v>15687.5</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" si="11"/>
-        <v>14350</v>
+        <v>14550</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" si="12"/>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="H22" s="1">
         <f t="shared" si="1"/>
-        <v>12340</v>
+        <v>12540</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="2"/>
-        <v>16862.5</v>
+        <v>17062.5</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" si="11"/>
-        <v>15450</v>
+        <v>15650</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" si="12"/>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="H23" s="1">
         <f t="shared" si="1"/>
-        <v>13220</v>
+        <v>13420</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="2"/>
-        <v>18237.5</v>
+        <v>18437.5</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1965,11 +1965,11 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" si="11"/>
-        <v>16550</v>
+        <v>16750</v>
       </c>
       <c r="E24" s="1">
         <f>D24*$I$3</f>
-        <v>23170</v>
+        <v>23450</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" si="12"/>
@@ -1977,11 +1977,11 @@
       </c>
       <c r="H24" s="1">
         <f t="shared" si="1"/>
-        <v>14100</v>
+        <v>14300</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="2"/>
-        <v>19612.5</v>
+        <v>19812.5</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D25" s="1">
         <f>D24+M$2</f>
-        <v>17750</v>
+        <v>17950</v>
       </c>
       <c r="F25" s="1">
         <f>F24+E$4-B$4</f>
@@ -2006,11 +2006,11 @@
       </c>
       <c r="H25" s="1">
         <f t="shared" si="1"/>
-        <v>15060</v>
+        <v>15260</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="2"/>
-        <v>21112.5</v>
+        <v>21312.5</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ref="D26:D28" si="13">D25+M$2</f>
-        <v>18950</v>
+        <v>19150</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" ref="F26:F29" si="14">F25+E$4-B$4</f>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="H26" s="1">
         <f t="shared" si="1"/>
-        <v>16020</v>
+        <v>16220</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="2"/>
-        <v>22612.5</v>
+        <v>22812.5</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" si="13"/>
-        <v>20150</v>
+        <v>20350</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" si="14"/>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
-        <v>16980</v>
+        <v>17180</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="2"/>
-        <v>24112.5</v>
+        <v>24312.5</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" si="13"/>
-        <v>21350</v>
+        <v>21550</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" si="14"/>
@@ -2093,11 +2093,11 @@
       </c>
       <c r="H28" s="1">
         <f t="shared" si="1"/>
-        <v>17940</v>
+        <v>18140</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="2"/>
-        <v>25612.5</v>
+        <v>25812.5</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -2114,11 +2114,11 @@
       </c>
       <c r="D29" s="1">
         <f>D28+M$2</f>
-        <v>22550</v>
+        <v>22750</v>
       </c>
       <c r="E29" s="1">
         <f>D29*$I$3</f>
-        <v>31569.999999999996</v>
+        <v>31849.999999999996</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" si="14"/>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="H29" s="1">
         <f t="shared" si="1"/>
-        <v>18900</v>
+        <v>19100</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="2"/>
-        <v>27112.5</v>
+        <v>27312.5</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:D33" si="16">D29+N$2</f>
-        <v>23750</v>
+        <v>23950</v>
       </c>
       <c r="F30" s="1">
         <f>F29+F$4-C$4</f>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="H30" s="1">
         <f t="shared" si="1"/>
-        <v>19860</v>
+        <v>20060</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="2"/>
-        <v>28612.5</v>
+        <v>28812.5</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" si="16"/>
-        <v>24950</v>
+        <v>25150</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" ref="F31:F34" si="18">F30+F$4-C$4</f>
@@ -2184,11 +2184,11 @@
       </c>
       <c r="H31" s="1">
         <f t="shared" si="1"/>
-        <v>20820</v>
+        <v>21020</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="2"/>
-        <v>30112.5</v>
+        <v>30312.5</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" si="16"/>
-        <v>26150</v>
+        <v>26350</v>
       </c>
       <c r="F32" s="1">
         <f t="shared" si="18"/>
@@ -2213,11 +2213,11 @@
       </c>
       <c r="H32" s="1">
         <f t="shared" si="1"/>
-        <v>21780</v>
+        <v>21980</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" si="2"/>
-        <v>31612.5</v>
+        <v>31812.5</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" si="16"/>
-        <v>27350</v>
+        <v>27550</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" si="18"/>
@@ -2242,11 +2242,11 @@
       </c>
       <c r="H33" s="1">
         <f t="shared" si="1"/>
-        <v>22740</v>
+        <v>22940</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="2"/>
-        <v>33112.5</v>
+        <v>33312.5</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="D34" s="1">
         <f>D33+N$2</f>
-        <v>28550</v>
+        <v>28750</v>
       </c>
       <c r="E34" s="1">
         <f>D34*$I$3</f>
-        <v>39970</v>
+        <v>40250</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" si="18"/>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="H34" s="1">
         <f t="shared" si="1"/>
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="2"/>
-        <v>34612.5</v>
+        <v>34812.5</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ref="D35:D38" si="19">D34+O$2</f>
-        <v>29750</v>
+        <v>29950</v>
       </c>
       <c r="F35" s="1">
         <f>F34+G$4-D$4</f>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="H35" s="1">
         <f t="shared" si="1"/>
-        <v>24660</v>
+        <v>24860</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="2"/>
-        <v>36112.5</v>
+        <v>36312.5</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" si="19"/>
-        <v>30950</v>
+        <v>31150</v>
       </c>
       <c r="F36" s="1">
         <f t="shared" ref="F36:F39" si="21">F35+G$4-D$4</f>
@@ -2333,11 +2333,11 @@
       </c>
       <c r="H36" s="1">
         <f t="shared" si="1"/>
-        <v>25620</v>
+        <v>25820</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="2"/>
-        <v>37612.5</v>
+        <v>37812.5</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" si="19"/>
-        <v>32150</v>
+        <v>32350</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" si="21"/>
@@ -2362,11 +2362,11 @@
       </c>
       <c r="H37" s="1">
         <f t="shared" si="1"/>
-        <v>26580</v>
+        <v>26780</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="2"/>
-        <v>39112.5</v>
+        <v>39312.5</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D38" s="1">
         <f t="shared" si="19"/>
-        <v>33350</v>
+        <v>33550</v>
       </c>
       <c r="F38" s="1">
         <f t="shared" si="21"/>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="H38" s="1">
         <f t="shared" si="1"/>
-        <v>27540</v>
+        <v>27740</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="2"/>
-        <v>40612.5</v>
+        <v>40812.5</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2412,11 +2412,11 @@
       </c>
       <c r="D39" s="1">
         <f>D38+O$2</f>
-        <v>34550</v>
+        <v>34750</v>
       </c>
       <c r="E39" s="1">
         <f>D39*$I$3</f>
-        <v>48370</v>
+        <v>48650</v>
       </c>
       <c r="F39" s="1">
         <f t="shared" si="21"/>
@@ -2424,11 +2424,11 @@
       </c>
       <c r="H39" s="1">
         <f t="shared" si="1"/>
-        <v>28500</v>
+        <v>28700</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="2"/>
-        <v>42112.5</v>
+        <v>42312.5</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D40" s="1">
         <f t="shared" ref="D40:D47" si="22">D39+P$2</f>
-        <v>35950</v>
+        <v>36150</v>
       </c>
       <c r="F40" s="1">
         <f>F39+H$4-E$4</f>
@@ -2453,11 +2453,11 @@
       </c>
       <c r="H40" s="1">
         <f t="shared" si="1"/>
-        <v>29620</v>
+        <v>29820</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="2"/>
-        <v>43862.5</v>
+        <v>44062.5</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" si="22"/>
-        <v>37350</v>
+        <v>37550</v>
       </c>
       <c r="F41" s="1">
         <f t="shared" ref="F41:F44" si="24">F40+H$4-E$4</f>
@@ -2482,11 +2482,11 @@
       </c>
       <c r="H41" s="1">
         <f t="shared" si="1"/>
-        <v>30740</v>
+        <v>30940</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="2"/>
-        <v>45612.5</v>
+        <v>45812.5</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D42" s="1">
         <f t="shared" si="22"/>
-        <v>38750</v>
+        <v>38950</v>
       </c>
       <c r="F42" s="1">
         <f t="shared" si="24"/>
@@ -2511,11 +2511,11 @@
       </c>
       <c r="H42" s="1">
         <f t="shared" si="1"/>
-        <v>31860</v>
+        <v>32060</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="2"/>
-        <v>47362.5</v>
+        <v>47562.5</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="D43" s="1">
         <f t="shared" si="22"/>
-        <v>40150</v>
+        <v>40350</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" si="24"/>
@@ -2540,11 +2540,11 @@
       </c>
       <c r="H43" s="1">
         <f t="shared" si="1"/>
-        <v>32980</v>
+        <v>33180</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="2"/>
-        <v>49112.5</v>
+        <v>49312.5</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D44" s="1">
         <f t="shared" si="22"/>
-        <v>41550</v>
+        <v>41750</v>
       </c>
       <c r="F44" s="1">
         <f t="shared" si="24"/>
@@ -2569,11 +2569,11 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" si="1"/>
-        <v>34100</v>
+        <v>34300</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="2"/>
-        <v>50862.5</v>
+        <v>51062.5</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D45" s="1">
         <f t="shared" si="22"/>
-        <v>42950</v>
+        <v>43150</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D46" s="1">
         <f t="shared" si="22"/>
-        <v>44350</v>
+        <v>44550</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D47" s="1">
         <f t="shared" si="22"/>
-        <v>45750</v>
+        <v>45950</v>
       </c>
     </row>
   </sheetData>
